--- a/Task_Tracker.xlsx
+++ b/Task_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LapTrinhAI\ITA 108 - Dự án 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My Laptop\Desktop\duan1\Global-Surface-Temperature-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA98C858-61DB-4D69-8C3B-EAC84EC180F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB99C159-8CB1-4E45-9BF0-75A0D2462392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="162">
   <si>
     <t>Rossmann Store Sales - Project Timeline</t>
   </si>
@@ -439,33 +439,9 @@
     <t>Thành viên</t>
   </si>
   <si>
-    <t>Nguyễn Văn Long</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lóng</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lòng</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lọng</t>
-  </si>
-  <si>
     <t>Not Started - Chưa bắt đầu</t>
   </si>
   <si>
-    <t>In Progress - Đang thực hiện</t>
-  </si>
-  <si>
-    <t>Done - Hoàn thành</t>
-  </si>
-  <si>
-    <t>Blocked - Bị kẹt, Cần hỗ trợ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review - Đang review </t>
-  </si>
-  <si>
     <t>Tuần 1</t>
   </si>
   <si>
@@ -518,6 +494,21 @@
   </si>
   <si>
     <t>Chưa hoàn thành</t>
+  </si>
+  <si>
+    <t>Lương Minh Kiệt</t>
+  </si>
+  <si>
+    <t>Cao Tấn Phát</t>
+  </si>
+  <si>
+    <t>Trần Duy Ân</t>
+  </si>
+  <si>
+    <t>Vòng Tín Phú</t>
+  </si>
+  <si>
+    <t>Lê Bá Hiền</t>
   </si>
 </sst>
 </file>
@@ -1011,21 +1002,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="46.06640625" customWidth="1"/>
-    <col min="4" max="4" width="17.06640625" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>1</v>
       </c>
@@ -1039,7 +1030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>5</v>
       </c>
@@ -1053,7 +1044,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>8</v>
       </c>
@@ -1064,10 +1055,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>11</v>
       </c>
@@ -1078,52 +1069,52 @@
         <v>13</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
-    <row r="8" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
-    <row r="9" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
     </row>
-    <row r="10" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="11" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
     </row>
-    <row r="13" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
-    <row r="14" spans="1:4" ht="20.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:4" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -1137,21 +1128,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I100"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.9296875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="46.06640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.86328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.53125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="8" style="3" customWidth="1"/>
+    <col min="2" max="2" width="46" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="8" customWidth="1"/>
     <col min="5" max="5" width="24" style="3" customWidth="1"/>
-    <col min="6" max="6" width="27.796875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.73046875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="25.265625" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="3"/>
+    <col min="6" max="6" width="27.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.28515625" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1180,7 +1171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
@@ -1197,7 +1188,7 @@
         <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G2" s="22">
         <v>478834</v>
@@ -1207,7 +1198,7 @@
       </c>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>26</v>
       </c>
@@ -1224,7 +1215,7 @@
         <v>27</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
@@ -1232,7 +1223,7 @@
       </c>
       <c r="I3" s="14"/>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>40</v>
       </c>
@@ -1249,7 +1240,7 @@
         <v>24</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
@@ -1257,7 +1248,7 @@
       </c>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>42</v>
       </c>
@@ -1274,7 +1265,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
@@ -1282,7 +1273,7 @@
       </c>
       <c r="I5" s="14"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>44</v>
       </c>
@@ -1299,7 +1290,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
@@ -1307,7 +1298,7 @@
       </c>
       <c r="I6" s="14"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>47</v>
       </c>
@@ -1324,7 +1315,7 @@
         <v>49</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
@@ -1332,7 +1323,7 @@
       </c>
       <c r="I7" s="14"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>50</v>
       </c>
@@ -1349,7 +1340,7 @@
         <v>49</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
@@ -1357,7 +1348,7 @@
       </c>
       <c r="I8" s="14"/>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>53</v>
       </c>
@@ -1374,7 +1365,7 @@
         <v>49</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
@@ -1382,7 +1373,7 @@
       </c>
       <c r="I9" s="14"/>
     </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>56</v>
       </c>
@@ -1399,7 +1390,7 @@
         <v>49</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
@@ -1407,7 +1398,7 @@
       </c>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>58</v>
       </c>
@@ -1424,7 +1415,7 @@
         <v>49</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
@@ -1432,7 +1423,7 @@
       </c>
       <c r="I11" s="14"/>
     </row>
-    <row r="12" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>60</v>
       </c>
@@ -1449,7 +1440,7 @@
         <v>49</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
@@ -1457,7 +1448,7 @@
       </c>
       <c r="I12" s="14"/>
     </row>
-    <row r="13" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>63</v>
       </c>
@@ -1474,7 +1465,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
@@ -1482,7 +1473,7 @@
       </c>
       <c r="I13" s="14"/>
     </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
@@ -1499,7 +1490,7 @@
         <v>49</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
@@ -1507,7 +1498,7 @@
       </c>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>68</v>
       </c>
@@ -1524,7 +1515,7 @@
         <v>49</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
@@ -1532,7 +1523,7 @@
       </c>
       <c r="I15" s="14"/>
     </row>
-    <row r="16" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>70</v>
       </c>
@@ -1549,7 +1540,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
@@ -1557,7 +1548,7 @@
       </c>
       <c r="I16" s="14"/>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>73</v>
       </c>
@@ -1574,7 +1565,7 @@
         <v>77</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
@@ -1582,7 +1573,7 @@
       </c>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>78</v>
       </c>
@@ -1599,7 +1590,7 @@
         <v>77</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
@@ -1607,7 +1598,7 @@
       </c>
       <c r="I18" s="15"/>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>80</v>
       </c>
@@ -1624,7 +1615,7 @@
         <v>77</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11" t="s">
@@ -1632,7 +1623,7 @@
       </c>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>82</v>
       </c>
@@ -1649,7 +1640,7 @@
         <v>77</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
@@ -1657,7 +1648,7 @@
       </c>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>85</v>
       </c>
@@ -1674,7 +1665,7 @@
         <v>77</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="11" t="s">
@@ -1682,7 +1673,7 @@
       </c>
       <c r="I21" s="15"/>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>87</v>
       </c>
@@ -1699,7 +1690,7 @@
         <v>77</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
@@ -1707,7 +1698,7 @@
       </c>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>90</v>
       </c>
@@ -1724,7 +1715,7 @@
         <v>77</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
@@ -1732,7 +1723,7 @@
       </c>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>92</v>
       </c>
@@ -1749,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
@@ -1757,7 +1748,7 @@
       </c>
       <c r="I24" s="15"/>
     </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>95</v>
       </c>
@@ -1774,7 +1765,7 @@
         <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
@@ -1782,7 +1773,7 @@
       </c>
       <c r="I25" s="14"/>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>99</v>
       </c>
@@ -1799,7 +1790,7 @@
         <v>98</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9" t="s">
@@ -1807,7 +1798,7 @@
       </c>
       <c r="I26" s="14"/>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>101</v>
       </c>
@@ -1824,7 +1815,7 @@
         <v>98</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
@@ -1832,7 +1823,7 @@
       </c>
       <c r="I27" s="14"/>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>104</v>
       </c>
@@ -1849,7 +1840,7 @@
         <v>98</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
@@ -1857,7 +1848,7 @@
       </c>
       <c r="I28" s="14"/>
     </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>106</v>
       </c>
@@ -1874,7 +1865,7 @@
         <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
@@ -1882,7 +1873,7 @@
       </c>
       <c r="I29" s="14"/>
     </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>110</v>
       </c>
@@ -1899,7 +1890,7 @@
         <v>109</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
@@ -1907,7 +1898,7 @@
       </c>
       <c r="I30" s="14"/>
     </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>112</v>
       </c>
@@ -1924,7 +1915,7 @@
         <v>109</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
@@ -1932,7 +1923,7 @@
       </c>
       <c r="I31" s="14"/>
     </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>115</v>
       </c>
@@ -1949,7 +1940,7 @@
         <v>109</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
@@ -1957,7 +1948,7 @@
       </c>
       <c r="I32" s="14"/>
     </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>117</v>
       </c>
@@ -1974,7 +1965,7 @@
         <v>27</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
@@ -1982,7 +1973,7 @@
       </c>
       <c r="I33" s="14"/>
     </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>120</v>
       </c>
@@ -1999,7 +1990,7 @@
         <v>24</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
@@ -2007,7 +1998,7 @@
       </c>
       <c r="I34" s="14"/>
     </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>122</v>
       </c>
@@ -2024,7 +2015,7 @@
         <v>27</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
@@ -2032,7 +2023,7 @@
       </c>
       <c r="I35" s="14"/>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>124</v>
       </c>
@@ -2049,7 +2040,7 @@
         <v>27</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
@@ -2057,7 +2048,7 @@
       </c>
       <c r="I36" s="14"/>
     </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>127</v>
       </c>
@@ -2074,7 +2065,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
@@ -2082,7 +2073,7 @@
       </c>
       <c r="I37" s="14"/>
     </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>130</v>
       </c>
@@ -2099,7 +2090,7 @@
         <v>24</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
@@ -2107,7 +2098,7 @@
       </c>
       <c r="I38" s="14"/>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>132</v>
       </c>
@@ -2124,7 +2115,7 @@
         <v>27</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
@@ -2132,7 +2123,7 @@
       </c>
       <c r="I39" s="14"/>
     </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>134</v>
       </c>
@@ -2149,7 +2140,7 @@
         <v>24</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
@@ -2157,7 +2148,7 @@
       </c>
       <c r="I40" s="14"/>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>28</v>
       </c>
@@ -2174,7 +2165,7 @@
         <v>27</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9" t="s">
@@ -2182,7 +2173,7 @@
       </c>
       <c r="I41" s="14"/>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="13"/>
@@ -2193,7 +2184,7 @@
       <c r="H42" s="16"/>
       <c r="I42" s="16"/>
     </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="13"/>
@@ -2204,7 +2195,7 @@
       <c r="H43" s="16"/>
       <c r="I43" s="16"/>
     </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="13"/>
@@ -2215,7 +2206,7 @@
       <c r="H44" s="16"/>
       <c r="I44" s="16"/>
     </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="13"/>
@@ -2226,7 +2217,7 @@
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="13"/>
@@ -2237,7 +2228,7 @@
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
     </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="13"/>
@@ -2248,7 +2239,7 @@
       <c r="H47" s="16"/>
       <c r="I47" s="16"/>
     </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="13"/>
@@ -2259,7 +2250,7 @@
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="13"/>
@@ -2270,7 +2261,7 @@
       <c r="H49" s="16"/>
       <c r="I49" s="16"/>
     </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="13"/>
@@ -2281,7 +2272,7 @@
       <c r="H50" s="16"/>
       <c r="I50" s="16"/>
     </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="13"/>
@@ -2292,7 +2283,7 @@
       <c r="H51" s="16"/>
       <c r="I51" s="16"/>
     </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="13"/>
@@ -2303,7 +2294,7 @@
       <c r="H52" s="16"/>
       <c r="I52" s="16"/>
     </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="13"/>
@@ -2314,7 +2305,7 @@
       <c r="H53" s="16"/>
       <c r="I53" s="16"/>
     </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="13"/>
@@ -2325,7 +2316,7 @@
       <c r="H54" s="16"/>
       <c r="I54" s="16"/>
     </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="13"/>
@@ -2336,7 +2327,7 @@
       <c r="H55" s="16"/>
       <c r="I55" s="16"/>
     </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="13"/>
@@ -2347,7 +2338,7 @@
       <c r="H56" s="16"/>
       <c r="I56" s="16"/>
     </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="13"/>
@@ -2358,7 +2349,7 @@
       <c r="H57" s="16"/>
       <c r="I57" s="16"/>
     </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="13"/>
@@ -2369,7 +2360,7 @@
       <c r="H58" s="16"/>
       <c r="I58" s="16"/>
     </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="13"/>
@@ -2380,7 +2371,7 @@
       <c r="H59" s="16"/>
       <c r="I59" s="16"/>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="13"/>
@@ -2391,7 +2382,7 @@
       <c r="H60" s="16"/>
       <c r="I60" s="16"/>
     </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="13"/>
@@ -2402,7 +2393,7 @@
       <c r="H61" s="16"/>
       <c r="I61" s="16"/>
     </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="13"/>
@@ -2413,7 +2404,7 @@
       <c r="H62" s="16"/>
       <c r="I62" s="16"/>
     </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="13"/>
@@ -2424,7 +2415,7 @@
       <c r="H63" s="16"/>
       <c r="I63" s="16"/>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="13"/>
@@ -2435,7 +2426,7 @@
       <c r="H64" s="16"/>
       <c r="I64" s="16"/>
     </row>
-    <row r="65" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="13"/>
@@ -2446,7 +2437,7 @@
       <c r="H65" s="16"/>
       <c r="I65" s="16"/>
     </row>
-    <row r="66" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="13"/>
@@ -2457,7 +2448,7 @@
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
     </row>
-    <row r="67" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="13"/>
@@ -2468,7 +2459,7 @@
       <c r="H67" s="16"/>
       <c r="I67" s="16"/>
     </row>
-    <row r="68" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="13"/>
@@ -2479,7 +2470,7 @@
       <c r="H68" s="16"/>
       <c r="I68" s="16"/>
     </row>
-    <row r="69" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="13"/>
@@ -2490,7 +2481,7 @@
       <c r="H69" s="16"/>
       <c r="I69" s="16"/>
     </row>
-    <row r="70" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="13"/>
@@ -2501,7 +2492,7 @@
       <c r="H70" s="16"/>
       <c r="I70" s="16"/>
     </row>
-    <row r="71" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="13"/>
@@ -2512,7 +2503,7 @@
       <c r="H71" s="16"/>
       <c r="I71" s="16"/>
     </row>
-    <row r="72" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="13"/>
@@ -2523,7 +2514,7 @@
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
     </row>
-    <row r="73" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="13"/>
@@ -2534,7 +2525,7 @@
       <c r="H73" s="16"/>
       <c r="I73" s="16"/>
     </row>
-    <row r="74" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="16"/>
       <c r="B74" s="16"/>
       <c r="C74" s="13"/>
@@ -2545,7 +2536,7 @@
       <c r="H74" s="16"/>
       <c r="I74" s="16"/>
     </row>
-    <row r="75" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
       <c r="B75" s="16"/>
       <c r="C75" s="13"/>
@@ -2556,7 +2547,7 @@
       <c r="H75" s="16"/>
       <c r="I75" s="16"/>
     </row>
-    <row r="76" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="B76" s="16"/>
       <c r="C76" s="13"/>
@@ -2567,7 +2558,7 @@
       <c r="H76" s="16"/>
       <c r="I76" s="16"/>
     </row>
-    <row r="77" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="B77" s="16"/>
       <c r="C77" s="13"/>
@@ -2578,7 +2569,7 @@
       <c r="H77" s="16"/>
       <c r="I77" s="16"/>
     </row>
-    <row r="78" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="B78" s="16"/>
       <c r="C78" s="13"/>
@@ -2589,7 +2580,7 @@
       <c r="H78" s="16"/>
       <c r="I78" s="16"/>
     </row>
-    <row r="79" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="16"/>
       <c r="C79" s="13"/>
@@ -2600,7 +2591,7 @@
       <c r="H79" s="16"/>
       <c r="I79" s="16"/>
     </row>
-    <row r="80" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="B80" s="16"/>
       <c r="C80" s="13"/>
@@ -2611,7 +2602,7 @@
       <c r="H80" s="16"/>
       <c r="I80" s="16"/>
     </row>
-    <row r="81" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
       <c r="C81" s="13"/>
@@ -2622,7 +2613,7 @@
       <c r="H81" s="16"/>
       <c r="I81" s="16"/>
     </row>
-    <row r="82" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="B82" s="16"/>
       <c r="C82" s="13"/>
@@ -2633,7 +2624,7 @@
       <c r="H82" s="16"/>
       <c r="I82" s="16"/>
     </row>
-    <row r="83" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="16"/>
       <c r="B83" s="16"/>
       <c r="C83" s="13"/>
@@ -2644,7 +2635,7 @@
       <c r="H83" s="16"/>
       <c r="I83" s="16"/>
     </row>
-    <row r="84" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16"/>
       <c r="B84" s="16"/>
       <c r="C84" s="13"/>
@@ -2655,7 +2646,7 @@
       <c r="H84" s="16"/>
       <c r="I84" s="16"/>
     </row>
-    <row r="85" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="16"/>
       <c r="B85" s="16"/>
       <c r="C85" s="13"/>
@@ -2666,7 +2657,7 @@
       <c r="H85" s="16"/>
       <c r="I85" s="16"/>
     </row>
-    <row r="86" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="16"/>
       <c r="B86" s="16"/>
       <c r="C86" s="13"/>
@@ -2677,7 +2668,7 @@
       <c r="H86" s="16"/>
       <c r="I86" s="16"/>
     </row>
-    <row r="87" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="B87" s="16"/>
       <c r="C87" s="13"/>
@@ -2688,7 +2679,7 @@
       <c r="H87" s="16"/>
       <c r="I87" s="16"/>
     </row>
-    <row r="88" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="B88" s="16"/>
       <c r="C88" s="13"/>
@@ -2699,7 +2690,7 @@
       <c r="H88" s="16"/>
       <c r="I88" s="16"/>
     </row>
-    <row r="89" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" s="16"/>
       <c r="C89" s="13"/>
@@ -2710,7 +2701,7 @@
       <c r="H89" s="16"/>
       <c r="I89" s="16"/>
     </row>
-    <row r="90" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" s="16"/>
       <c r="C90" s="13"/>
@@ -2721,7 +2712,7 @@
       <c r="H90" s="16"/>
       <c r="I90" s="16"/>
     </row>
-    <row r="91" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="B91" s="16"/>
       <c r="C91" s="13"/>
@@ -2732,7 +2723,7 @@
       <c r="H91" s="16"/>
       <c r="I91" s="16"/>
     </row>
-    <row r="92" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" s="16"/>
       <c r="C92" s="13"/>
@@ -2743,7 +2734,7 @@
       <c r="H92" s="16"/>
       <c r="I92" s="16"/>
     </row>
-    <row r="93" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="16"/>
       <c r="B93" s="16"/>
       <c r="C93" s="13"/>
@@ -2754,7 +2745,7 @@
       <c r="H93" s="16"/>
       <c r="I93" s="16"/>
     </row>
-    <row r="94" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" s="16"/>
       <c r="C94" s="13"/>
@@ -2765,7 +2756,7 @@
       <c r="H94" s="16"/>
       <c r="I94" s="16"/>
     </row>
-    <row r="95" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="B95" s="16"/>
       <c r="C95" s="13"/>
@@ -2776,7 +2767,7 @@
       <c r="H95" s="16"/>
       <c r="I95" s="16"/>
     </row>
-    <row r="96" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" s="16"/>
       <c r="C96" s="13"/>
@@ -2787,7 +2778,7 @@
       <c r="H96" s="16"/>
       <c r="I96" s="16"/>
     </row>
-    <row r="97" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" s="16"/>
       <c r="C97" s="13"/>
@@ -2798,7 +2789,7 @@
       <c r="H97" s="16"/>
       <c r="I97" s="16"/>
     </row>
-    <row r="98" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="16"/>
       <c r="B98" s="16"/>
       <c r="C98" s="13"/>
@@ -2809,7 +2800,7 @@
       <c r="H98" s="16"/>
       <c r="I98" s="16"/>
     </row>
-    <row r="99" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="16"/>
       <c r="B99" s="16"/>
       <c r="C99" s="13"/>
@@ -2820,7 +2811,7 @@
       <c r="H99" s="16"/>
       <c r="I99" s="16"/>
     </row>
-    <row r="100" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" s="6" customFormat="1" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" s="16"/>
       <c r="C100" s="13"/>
@@ -2857,19 +2848,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.46484375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="42.9296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="34.06640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="35.06640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.19921875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="43" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" style="3" customWidth="1"/>
     <col min="7" max="9" width="25" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="3"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>31</v>
       </c>
@@ -2879,8 +2870,8 @@
       <c r="E1" s="26"/>
       <c r="F1" s="26"/>
     </row>
-    <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>32</v>
       </c>
@@ -2900,67 +2891,67 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="D5" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="E5" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="F5" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="24" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="B6" s="24" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="24" t="s">
+      <c r="C6" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="D6" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="E6" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>163</v>
-      </c>
       <c r="F6" s="24" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
@@ -2968,7 +2959,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
     </row>
-    <row r="8" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -2976,7 +2967,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
     </row>
-    <row r="9" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -2984,7 +2975,7 @@
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
     </row>
-    <row r="10" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -2992,7 +2983,7 @@
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
     </row>
-    <row r="11" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -3000,7 +2991,7 @@
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
     </row>
-    <row r="12" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -3008,7 +2999,7 @@
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
     </row>
-    <row r="13" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -3016,7 +3007,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
     </row>
-    <row r="14" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -3024,7 +3015,7 @@
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
     </row>
-    <row r="15" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
@@ -3032,7 +3023,7 @@
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
     </row>
-    <row r="16" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
@@ -3040,7 +3031,7 @@
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
     </row>
-    <row r="17" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
@@ -3048,7 +3039,7 @@
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
     </row>
-    <row r="18" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -3056,7 +3047,7 @@
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
     </row>
-    <row r="19" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
@@ -3064,7 +3055,7 @@
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
     </row>
-    <row r="20" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -3072,7 +3063,7 @@
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
     </row>
-    <row r="21" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -3088,88 +3079,90 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2205233F-5B25-4195-8520-D0D25C8AE853}">
   <dimension ref="A11:A30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.1328125" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="17.649999999999999" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="17.649999999999999" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="17.649999999999999" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="17.649999999999999" x14ac:dyDescent="0.5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A16" s="20"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="20"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="20"/>
     </row>
-    <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="21"/>
     </row>
-    <row r="29" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="21"/>
     </row>
-    <row r="30" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="21"/>
     </row>
   </sheetData>
